--- a/lookup/edd_compounds.xlsx
+++ b/lookup/edd_compounds.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofmaine-my.sharepoint.com/personal/lucas_beem_maine_gov/Documents/Documents/Projects/refactor/lookup/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofmaine-my.sharepoint.com/personal/lucas_beem_maine_gov/Documents/Documents/refactor/lookup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="483" documentId="8_{8C560773-DE13-438E-BEBB-3ECB04085AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A01563A6-29EA-4EE7-AD05-15F4351F84C9}"/>
+  <xr:revisionPtr revIDLastSave="484" documentId="8_{8C560773-DE13-438E-BEBB-3ECB04085AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B3237B1-5227-41F4-B0C4-CBA788CAE6A5}"/>
   <bookViews>
-    <workbookView xWindow="-27630" yWindow="420" windowWidth="26370" windowHeight="12465" xr2:uid="{DA70FC4B-612E-43F0-A14B-187685F0EDFF}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{DA70FC4B-612E-43F0-A14B-187685F0EDFF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -440,9 +440,6 @@
     <t>NICKEL, TOTAL</t>
   </si>
   <si>
-    <t>NITROGEN, AMMONIA as N</t>
-  </si>
-  <si>
     <t>NITROGEN, NITRITE as N</t>
   </si>
   <si>
@@ -1380,6 +1377,9 @@
   </si>
   <si>
     <t>equivalent_carbon</t>
+  </si>
+  <si>
+    <t>NITROGEN, AMMONIA AS N</t>
   </si>
 </sst>
 </file>
@@ -1792,7 +1792,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
@@ -1807,43 +1807,43 @@
         <v>8</v>
       </c>
       <c r="K1" t="s">
+        <v>422</v>
+      </c>
+      <c r="L1" t="s">
         <v>423</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>424</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>425</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>426</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>427</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>428</v>
       </c>
-      <c r="Q1" t="s">
-        <v>429</v>
-      </c>
       <c r="R1" t="s">
+        <v>432</v>
+      </c>
+      <c r="S1" t="s">
+        <v>434</v>
+      </c>
+      <c r="T1" t="s">
         <v>433</v>
       </c>
-      <c r="S1" t="s">
-        <v>435</v>
-      </c>
-      <c r="T1" t="s">
-        <v>434</v>
-      </c>
       <c r="U1" t="s">
+        <v>443</v>
+      </c>
+      <c r="V1" t="s">
         <v>444</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>445</v>
-      </c>
-      <c r="W1" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
@@ -1854,19 +1854,19 @@
         <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
@@ -1896,42 +1896,42 @@
         <v>0</v>
       </c>
       <c r="S2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B3">
         <v>290</v>
       </c>
       <c r="C3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H3" t="s">
         <v>10</v>
@@ -1961,42 +1961,42 @@
         <v>0</v>
       </c>
       <c r="S3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B4">
         <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H4" t="s">
         <v>12</v>
@@ -2026,42 +2026,42 @@
         <v>0</v>
       </c>
       <c r="S4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H5" t="s">
         <v>13</v>
@@ -2091,42 +2091,42 @@
         <v>0</v>
       </c>
       <c r="S5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B6">
         <v>8000</v>
       </c>
       <c r="C6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H6" t="s">
         <v>14</v>
@@ -2156,42 +2156,42 @@
         <v>0</v>
       </c>
       <c r="S6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B7">
         <v>5.7</v>
       </c>
       <c r="C7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -2221,42 +2221,42 @@
         <v>0</v>
       </c>
       <c r="S7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B8">
         <v>0.42</v>
       </c>
       <c r="C8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
@@ -2286,42 +2286,42 @@
         <v>0</v>
       </c>
       <c r="S8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B9">
         <v>0.76</v>
       </c>
       <c r="C9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H9" t="s">
         <v>17</v>
@@ -2351,42 +2351,42 @@
         <v>0</v>
       </c>
       <c r="S9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B10">
         <v>3.3E-3</v>
       </c>
       <c r="C10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H10" t="s">
         <v>18</v>
@@ -2416,42 +2416,42 @@
         <v>0</v>
       </c>
       <c r="S10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B11">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="C11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -2481,42 +2481,42 @@
         <v>0</v>
       </c>
       <c r="S11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B12">
         <v>300</v>
       </c>
       <c r="C12" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D12" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E12" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F12" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G12" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H12" t="s">
         <v>20</v>
@@ -2546,42 +2546,42 @@
         <v>0</v>
       </c>
       <c r="S12" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T12" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U12" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V12" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W12" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B13">
         <v>1.7</v>
       </c>
       <c r="C13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H13" t="s">
         <v>21</v>
@@ -2611,42 +2611,42 @@
         <v>0</v>
       </c>
       <c r="S13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B14">
         <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D14" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E14" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F14" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G14" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H14" t="s">
         <v>22</v>
@@ -2679,42 +2679,42 @@
         <v>0</v>
       </c>
       <c r="S14" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T14" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U14" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V14" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W14" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B15">
         <v>8.3000000000000007</v>
       </c>
       <c r="C15" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D15" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E15" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F15" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G15" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H15" t="s">
         <v>23</v>
@@ -2744,42 +2744,42 @@
         <v>0</v>
       </c>
       <c r="S15" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T15" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U15" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V15" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W15" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B16">
         <v>7</v>
       </c>
       <c r="C16" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D16" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E16" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F16" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G16" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H16" t="s">
         <v>24</v>
@@ -2809,42 +2809,42 @@
         <v>0</v>
       </c>
       <c r="S16" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T16" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U16" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V16" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W16" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B17">
         <v>7.4999999999999997E-3</v>
       </c>
       <c r="C17" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D17" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E17" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F17" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G17" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H17" t="s">
         <v>25</v>
@@ -2874,42 +2874,42 @@
         <v>0</v>
       </c>
       <c r="S17" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T17" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U17" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V17" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W17" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B18">
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D18" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E18" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F18" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G18" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H18" t="s">
         <v>26</v>
@@ -2939,42 +2939,42 @@
         <v>0</v>
       </c>
       <c r="S18" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T18" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U18" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V18" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W18" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B19">
         <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D19" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E19" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F19" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G19" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H19" t="s">
         <v>27</v>
@@ -3004,42 +3004,42 @@
         <v>0</v>
       </c>
       <c r="S19" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T19" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U19" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V19" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W19" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B20">
         <v>0.17</v>
       </c>
       <c r="C20" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D20" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E20" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F20" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G20" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H20" t="s">
         <v>28</v>
@@ -3069,42 +3069,42 @@
         <v>0</v>
       </c>
       <c r="S20" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T20" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U20" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V20" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W20" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B21">
         <v>300</v>
       </c>
       <c r="C21" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D21" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E21" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F21" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G21" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H21" t="s">
         <v>29</v>
@@ -3134,42 +3134,42 @@
         <v>0</v>
       </c>
       <c r="S21" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T21" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U21" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V21" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W21" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B22">
         <v>370</v>
       </c>
       <c r="C22" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D22" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E22" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F22" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G22" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H22" t="s">
         <v>30</v>
@@ -3202,42 +3202,42 @@
         <v>0</v>
       </c>
       <c r="S22" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T22" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U22" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V22" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W22" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B23">
         <v>4.7</v>
       </c>
       <c r="C23" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D23" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E23" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F23" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G23" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H23" t="s">
         <v>91</v>
@@ -3270,42 +3270,42 @@
         <v>0</v>
       </c>
       <c r="S23" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T23" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U23" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V23" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W23" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B24">
         <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D24" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E24" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F24" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G24" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H24" t="s">
         <v>32</v>
@@ -3335,42 +3335,42 @@
         <v>0</v>
       </c>
       <c r="S24" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T24" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U24" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V24" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W24" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B25">
         <v>4.8</v>
       </c>
       <c r="C25" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D25" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E25" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F25" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G25" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H25" t="s">
         <v>33</v>
@@ -3400,42 +3400,42 @@
         <v>0</v>
       </c>
       <c r="S25" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T25" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U25" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V25" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W25" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B26">
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="C26" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D26" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E26" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F26" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G26" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H26" t="s">
         <v>34</v>
@@ -3465,42 +3465,42 @@
         <v>0</v>
       </c>
       <c r="S26" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T26" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U26" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V26" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W26" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B27">
         <v>5600</v>
       </c>
       <c r="C27" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D27" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E27" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F27" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G27" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H27" t="s">
         <v>35</v>
@@ -3530,42 +3530,42 @@
         <v>0</v>
       </c>
       <c r="S27" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T27" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U27" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V27" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W27" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B28" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C28" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D28" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E28" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F28" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G28" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H28" t="s">
         <v>36</v>
@@ -3595,42 +3595,42 @@
         <v>0</v>
       </c>
       <c r="S28" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T28" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U28" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V28" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W28" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B29">
         <v>38</v>
       </c>
       <c r="C29" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D29" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E29" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F29" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G29" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H29" t="s">
         <v>37</v>
@@ -3660,24 +3660,24 @@
         <v>0</v>
       </c>
       <c r="S29" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T29" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U29" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V29" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W29" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B30">
         <v>36</v>
@@ -3695,7 +3695,7 @@
         <v>0.4</v>
       </c>
       <c r="G30" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H30" t="s">
         <v>38</v>
@@ -3725,13 +3725,13 @@
         <v>0</v>
       </c>
       <c r="S30" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T30" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U30" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V30">
         <v>11</v>
@@ -3742,25 +3742,25 @@
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B31" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C31" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D31" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E31" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F31" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G31" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H31" t="s">
         <v>39</v>
@@ -3790,42 +3790,42 @@
         <v>0</v>
       </c>
       <c r="S31" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T31" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U31" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V31" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W31" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B32" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C32" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D32" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E32" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F32" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G32" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H32" t="s">
         <v>40</v>
@@ -3855,42 +3855,42 @@
         <v>0</v>
       </c>
       <c r="S32" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T32" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U32" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V32" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W32" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B33">
         <v>6300</v>
       </c>
       <c r="C33" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D33" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E33" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F33" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G33" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H33" t="s">
         <v>41</v>
@@ -3920,24 +3920,24 @@
         <v>0</v>
       </c>
       <c r="S33" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T33" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U33" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V33" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W33" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B34">
         <v>540</v>
@@ -3955,7 +3955,7 @@
         <v>0.4</v>
       </c>
       <c r="G34" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H34" t="s">
         <v>42</v>
@@ -3985,13 +3985,13 @@
         <v>0</v>
       </c>
       <c r="S34" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T34" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U34" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V34">
         <v>12</v>
@@ -4002,7 +4002,7 @@
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B35">
         <v>520</v>
@@ -4020,7 +4020,7 @@
         <v>0.4</v>
       </c>
       <c r="G35" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H35" t="s">
         <v>43</v>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T35" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U35" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V35">
         <v>12</v>
@@ -4067,25 +4067,25 @@
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B36">
         <v>18000</v>
       </c>
       <c r="C36" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D36" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E36" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F36" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G36" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H36" t="s">
         <v>44</v>
@@ -4115,42 +4115,42 @@
         <v>0</v>
       </c>
       <c r="S36" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T36" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U36" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V36" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W36" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B37">
         <v>0.52</v>
       </c>
       <c r="C37" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D37" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E37" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F37" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G37" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H37" t="s">
         <v>45</v>
@@ -4180,42 +4180,42 @@
         <v>0</v>
       </c>
       <c r="S37" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T37" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U37" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V37" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W37" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H38" t="s">
         <v>46</v>
@@ -4245,48 +4245,48 @@
         <v>0</v>
       </c>
       <c r="S38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B39" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C39" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D39" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E39" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F39" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G39" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H39" t="s">
         <v>47</v>
       </c>
       <c r="I39" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K39">
         <v>0</v>
@@ -4313,42 +4313,42 @@
         <v>0</v>
       </c>
       <c r="S39" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T39" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U39" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V39" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W39" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B40">
         <v>20000</v>
       </c>
       <c r="C40" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D40" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E40" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F40" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G40" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H40" t="s">
         <v>48</v>
@@ -4378,45 +4378,45 @@
         <v>0</v>
       </c>
       <c r="S40" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T40" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U40" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V40" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W40" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H41" t="s">
-        <v>133</v>
+        <v>446</v>
       </c>
       <c r="I41" t="s">
         <v>49</v>
@@ -4446,24 +4446,24 @@
         <v>0</v>
       </c>
       <c r="S41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B42">
         <v>1800</v>
@@ -4472,7 +4472,7 @@
         <v>3200</v>
       </c>
       <c r="D42" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E42">
         <v>0.4</v>
@@ -4481,7 +4481,7 @@
         <v>0.4</v>
       </c>
       <c r="G42" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H42" t="s">
         <v>50</v>
@@ -4511,10 +4511,10 @@
         <v>0</v>
       </c>
       <c r="S42" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T42" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U42">
         <v>341.3</v>
@@ -4528,25 +4528,25 @@
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B43">
         <v>7.8</v>
       </c>
       <c r="C43" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D43" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E43" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F43" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G43" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H43" t="s">
         <v>51</v>
@@ -4576,42 +4576,42 @@
         <v>0</v>
       </c>
       <c r="S43" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T43" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U43" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V43" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W43" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B44">
         <v>0.52</v>
       </c>
       <c r="C44" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D44" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E44" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F44" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G44" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H44" t="s">
         <v>52</v>
@@ -4644,42 +4644,42 @@
         <v>1</v>
       </c>
       <c r="S44" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T44" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U44" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V44" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W44" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B45">
         <v>3800</v>
       </c>
       <c r="C45" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D45" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E45" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F45" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G45" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H45" t="s">
         <v>54</v>
@@ -4709,24 +4709,24 @@
         <v>0</v>
       </c>
       <c r="S45" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T45" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U45" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V45" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W45" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B46">
         <v>4.5999999999999996</v>
@@ -4738,13 +4738,13 @@
         <v>17</v>
       </c>
       <c r="E46" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F46" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G46" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H46" t="s">
         <v>55</v>
@@ -4774,13 +4774,13 @@
         <v>0</v>
       </c>
       <c r="S46" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T46" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U46" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V46">
         <v>6</v>
@@ -4791,7 +4791,7 @@
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B47">
         <v>0.3</v>
@@ -4809,7 +4809,7 @@
         <v>0.4</v>
       </c>
       <c r="G47" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H47" t="s">
         <v>56</v>
@@ -4839,13 +4839,13 @@
         <v>0</v>
       </c>
       <c r="S47" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T47" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U47" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V47">
         <v>18</v>
@@ -4856,7 +4856,7 @@
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B48">
         <v>0.25</v>
@@ -4874,7 +4874,7 @@
         <v>0.2</v>
       </c>
       <c r="G48" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H48" t="s">
         <v>57</v>
@@ -4904,10 +4904,10 @@
         <v>0</v>
       </c>
       <c r="S48" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T48" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U48">
         <v>495</v>
@@ -4921,7 +4921,7 @@
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B49">
         <v>2.5</v>
@@ -4939,7 +4939,7 @@
         <v>0.4</v>
       </c>
       <c r="G49" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H49" t="s">
         <v>58</v>
@@ -4969,13 +4969,13 @@
         <v>0</v>
       </c>
       <c r="S49" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T49" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U49" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V49">
         <v>20</v>
@@ -4986,7 +4986,7 @@
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B50">
         <v>600</v>
@@ -5004,7 +5004,7 @@
         <v>0.4</v>
       </c>
       <c r="G50" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H50" t="s">
         <v>59</v>
@@ -5034,13 +5034,13 @@
         <v>0</v>
       </c>
       <c r="S50" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T50" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U50" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V50">
         <v>22</v>
@@ -5051,7 +5051,7 @@
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B51">
         <v>25</v>
@@ -5069,7 +5069,7 @@
         <v>0.4</v>
       </c>
       <c r="G51" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H51" t="s">
         <v>60</v>
@@ -5099,13 +5099,13 @@
         <v>0</v>
       </c>
       <c r="S51" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T51" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U51" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V51">
         <v>20</v>
@@ -5116,25 +5116,25 @@
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B52">
         <v>25</v>
       </c>
       <c r="C52" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D52" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E52" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F52" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G52" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H52" t="s">
         <v>61</v>
@@ -5164,42 +5164,42 @@
         <v>0</v>
       </c>
       <c r="S52" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T52" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U52" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V52" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W52" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B53">
         <v>4000</v>
       </c>
       <c r="C53" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D53" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E53" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F53" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G53" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H53" t="s">
         <v>62</v>
@@ -5229,42 +5229,42 @@
         <v>0</v>
       </c>
       <c r="S53" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T53" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U53" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V53" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W53" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="54" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B54" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C54" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D54" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E54" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F54" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G54" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H54" t="s">
         <v>63</v>
@@ -5294,42 +5294,42 @@
         <v>0</v>
       </c>
       <c r="S54" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T54" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U54" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V54" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W54" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="55" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B55">
         <v>62</v>
       </c>
       <c r="C55" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D55" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E55" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F55" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G55" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H55" t="s">
         <v>64</v>
@@ -5359,42 +5359,42 @@
         <v>0</v>
       </c>
       <c r="S55" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T55" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U55" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V55" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W55" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B56">
         <v>83</v>
       </c>
       <c r="C56" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D56" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E56" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F56" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G56" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H56" t="s">
         <v>65</v>
@@ -5424,42 +5424,42 @@
         <v>0</v>
       </c>
       <c r="S56" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T56" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U56" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V56" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W56" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B57">
         <v>1.3</v>
       </c>
       <c r="C57" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D57" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E57" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F57" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G57" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H57" t="s">
         <v>66</v>
@@ -5489,42 +5489,42 @@
         <v>0</v>
       </c>
       <c r="S57" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T57" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U57" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V57" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W57" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="58" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B58">
         <v>33</v>
       </c>
       <c r="C58" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D58" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E58" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F58" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G58" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H58" t="s">
         <v>67</v>
@@ -5554,42 +5554,42 @@
         <v>0</v>
       </c>
       <c r="S58" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T58" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U58" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V58" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W58" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B59">
         <v>7.6</v>
       </c>
       <c r="C59" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D59" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E59" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F59" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G59" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H59" t="s">
         <v>68</v>
@@ -5619,24 +5619,24 @@
         <v>0</v>
       </c>
       <c r="S59" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T59" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U59" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V59" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W59" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B60">
         <v>180</v>
@@ -5648,13 +5648,13 @@
         <v>1700</v>
       </c>
       <c r="E60" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F60" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G60" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H60" t="s">
         <v>69</v>
@@ -5684,42 +5684,42 @@
         <v>0</v>
       </c>
       <c r="S60" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T60" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U60" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V60" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W60" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B61" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C61" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D61" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E61" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F61" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G61" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H61" t="s">
         <v>70</v>
@@ -5749,24 +5749,24 @@
         <v>0</v>
       </c>
       <c r="S61" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T61" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U61" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V61" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W61" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="62" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B62">
         <v>71</v>
@@ -5778,13 +5778,13 @@
         <v>660</v>
       </c>
       <c r="E62" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F62" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G62" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H62" t="s">
         <v>71</v>
@@ -5814,24 +5814,24 @@
         <v>0</v>
       </c>
       <c r="S62" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T62" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U62" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V62" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W62" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="63" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B63">
         <v>350</v>
@@ -5843,13 +5843,13 @@
         <v>2500</v>
       </c>
       <c r="E63" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F63" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G63" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H63" t="s">
         <v>72</v>
@@ -5879,42 +5879,42 @@
         <v>0</v>
       </c>
       <c r="S63" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T63" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U63" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V63" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W63" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B64" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C64" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D64" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E64" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F64" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G64" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H64" t="s">
         <v>73</v>
@@ -5944,24 +5944,24 @@
         <v>0</v>
       </c>
       <c r="S64" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T64" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U64" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V64" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W64" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B65">
         <v>350</v>
@@ -5979,7 +5979,7 @@
         <v>100</v>
       </c>
       <c r="G65" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H65" t="s">
         <v>74</v>
@@ -6009,24 +6009,24 @@
         <v>0</v>
       </c>
       <c r="S65" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T65" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U65" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V65" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W65" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B66">
         <v>600</v>
@@ -6044,7 +6044,7 @@
         <v>100</v>
       </c>
       <c r="G66" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H66" t="s">
         <v>75</v>
@@ -6074,33 +6074,33 @@
         <v>0</v>
       </c>
       <c r="S66" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T66" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U66" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V66" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W66" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B67">
         <v>40000</v>
       </c>
       <c r="C67" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D67" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E67">
         <v>100</v>
@@ -6109,7 +6109,7 @@
         <v>100</v>
       </c>
       <c r="G67" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H67" t="s">
         <v>76</v>
@@ -6139,42 +6139,42 @@
         <v>0</v>
       </c>
       <c r="S67" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T67" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U67" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V67" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W67" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B68">
         <v>1.8</v>
       </c>
       <c r="C68" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D68" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E68" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F68" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G68" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H68" t="s">
         <v>77</v>
@@ -6204,42 +6204,42 @@
         <v>0</v>
       </c>
       <c r="S68" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T68" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U68" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V68" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W68" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="69" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B69" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C69" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D69" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E69" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F69" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G69" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H69" t="s">
         <v>78</v>
@@ -6272,42 +6272,42 @@
         <v>1</v>
       </c>
       <c r="S69" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T69" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U69" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V69" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W69" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B70">
         <v>810</v>
       </c>
       <c r="C70" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D70" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E70" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F70" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G70" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H70" t="s">
         <v>80</v>
@@ -6337,42 +6337,42 @@
         <v>0</v>
       </c>
       <c r="S70" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T70" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U70" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V70" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W70" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="71" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B71">
         <v>4.5999999999999996</v>
       </c>
       <c r="C71" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D71" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E71" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F71" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G71" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H71" t="s">
         <v>81</v>
@@ -6402,42 +6402,42 @@
         <v>0</v>
       </c>
       <c r="S71" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T71" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U71" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V71" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W71" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B72" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C72" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D72" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E72" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F72" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G72" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H72" t="s">
         <v>82</v>
@@ -6467,42 +6467,42 @@
         <v>0</v>
       </c>
       <c r="S72" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T72" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U72" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V72" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W72" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B73" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C73" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D73" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E73" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F73" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G73" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H73" t="s">
         <v>83</v>
@@ -6532,42 +6532,42 @@
         <v>1</v>
       </c>
       <c r="S73" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T73" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U73" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V73" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W73" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="74" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B74">
         <v>78</v>
       </c>
       <c r="C74" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D74" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E74" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F74" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G74" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H74" t="s">
         <v>84</v>
@@ -6597,42 +6597,42 @@
         <v>0</v>
       </c>
       <c r="S74" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T74" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U74" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V74" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W74" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="75" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B75" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C75" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D75" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E75" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F75" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G75" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H75" t="s">
         <v>85</v>
@@ -6662,42 +6662,42 @@
         <v>0</v>
       </c>
       <c r="S75" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T75" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U75" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V75" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W75" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B76">
         <v>2.2000000000000002</v>
       </c>
       <c r="C76" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D76" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E76" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F76" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G76" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H76" t="s">
         <v>86</v>
@@ -6727,42 +6727,42 @@
         <v>0</v>
       </c>
       <c r="S76" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T76" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U76" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V76" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W76" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="77" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B77">
         <v>190</v>
       </c>
       <c r="C77" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D77" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E77" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F77" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G77" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H77" t="s">
         <v>87</v>
@@ -6792,42 +6792,42 @@
         <v>0</v>
       </c>
       <c r="S77" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T77" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U77" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V77" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W77" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="78" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B78">
         <v>0.35</v>
       </c>
       <c r="C78" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D78" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E78" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F78" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G78" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H78" t="s">
         <v>88</v>
@@ -6857,42 +6857,42 @@
         <v>0</v>
       </c>
       <c r="S78" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T78" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U78" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V78" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W78" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="79" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B79">
         <v>23000</v>
       </c>
       <c r="C79" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D79" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E79" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F79" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G79" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H79" t="s">
         <v>89</v>
@@ -6922,24 +6922,24 @@
         <v>0</v>
       </c>
       <c r="S79" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T79" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U79" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V79" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W79" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B80">
         <v>250</v>
@@ -6951,13 +6951,13 @@
         <v>1600</v>
       </c>
       <c r="E80" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F80" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G80" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H80" t="s">
         <v>90</v>
@@ -6987,13 +6987,13 @@
         <v>0</v>
       </c>
       <c r="S80" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T80" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U80" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V80">
         <v>18</v>
@@ -7004,31 +7004,31 @@
     </row>
     <row r="81" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B81" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C81" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D81" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E81" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F81" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G81" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H81" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I81" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K81">
         <v>0</v>
@@ -7055,42 +7055,42 @@
         <v>1</v>
       </c>
       <c r="S81" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T81" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U81" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V81" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W81" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="82" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B82">
         <v>6</v>
       </c>
       <c r="C82" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D82" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E82" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F82" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G82" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H82" t="s">
         <v>94</v>
@@ -7120,42 +7120,42 @@
         <v>0</v>
       </c>
       <c r="S82" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T82" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U82" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V82" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W82" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="83" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B83">
         <v>800</v>
       </c>
       <c r="C83" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D83" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E83" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F83" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G83" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H83" t="s">
         <v>95</v>
@@ -7188,24 +7188,24 @@
         <v>1</v>
       </c>
       <c r="S83" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T83" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U83" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V83" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W83" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B84">
         <v>0.25</v>
@@ -7223,7 +7223,7 @@
         <v>0.4</v>
       </c>
       <c r="G84" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H84" t="s">
         <v>97</v>
@@ -7253,13 +7253,13 @@
         <v>0</v>
       </c>
       <c r="S84" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T84" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U84" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V84">
         <v>22</v>
@@ -7270,25 +7270,25 @@
     </row>
     <row r="85" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B85">
         <v>8.6999999999999993</v>
       </c>
       <c r="C85" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D85" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E85" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F85" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G85" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H85" t="s">
         <v>98</v>
@@ -7318,42 +7318,42 @@
         <v>0</v>
       </c>
       <c r="S85" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T85" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U85" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V85" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W85" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="86" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B86">
         <v>8.3000000000000007</v>
       </c>
       <c r="C86" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D86" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E86" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F86" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G86" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H86" t="s">
         <v>99</v>
@@ -7383,42 +7383,42 @@
         <v>0</v>
       </c>
       <c r="S86" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T86" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U86" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V86" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W86" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B87">
         <v>200</v>
       </c>
       <c r="C87" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D87" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E87" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F87" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G87" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H87" t="s">
         <v>100</v>
@@ -7448,45 +7448,45 @@
         <v>0</v>
       </c>
       <c r="S87" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T87" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U87" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V87" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W87" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B88" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C88" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D88" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E88" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F88" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G88" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H88" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K88">
         <v>0</v>
@@ -7513,45 +7513,45 @@
         <v>0</v>
       </c>
       <c r="S88" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T88" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U88" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V88" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W88" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="89" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B89">
         <v>4.7</v>
       </c>
       <c r="C89" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D89" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E89" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F89" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G89" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H89" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K89">
         <v>0</v>
@@ -7578,42 +7578,42 @@
         <v>0</v>
       </c>
       <c r="S89" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T89" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U89" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V89" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W89" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="90" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B90" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C90" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D90" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E90" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F90" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G90" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H90" t="s">
         <v>101</v>
@@ -7643,48 +7643,48 @@
         <v>0</v>
       </c>
       <c r="S90" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T90" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U90" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V90" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W90" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="91" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B91" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C91" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D91" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E91" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F91" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G91" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H91" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I91" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K91">
         <v>0</v>
@@ -7711,48 +7711,48 @@
         <v>0</v>
       </c>
       <c r="S91" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T91" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U91" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V91" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W91" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="92" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B92" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C92" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D92" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E92" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F92" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G92" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H92" t="s">
         <v>102</v>
       </c>
       <c r="I92" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K92">
         <v>0</v>
@@ -7779,42 +7779,42 @@
         <v>1</v>
       </c>
       <c r="S92" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T92" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U92" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V92" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W92" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="93" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B93">
         <v>3900</v>
       </c>
       <c r="C93" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D93" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E93" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F93" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G93" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H93" t="s">
         <v>103</v>
@@ -7844,42 +7844,42 @@
         <v>0</v>
       </c>
       <c r="S93" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T93" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U93" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V93" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W93" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="94" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B94">
         <v>630</v>
       </c>
       <c r="C94" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D94" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E94" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F94" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G94" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H94" t="s">
         <v>104</v>
@@ -7909,24 +7909,24 @@
         <v>0</v>
       </c>
       <c r="S94" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T94" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U94" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V94" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W94" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="95" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B95">
         <v>15</v>
@@ -7938,13 +7938,13 @@
         <v>86</v>
       </c>
       <c r="E95" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F95" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G95" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H95" t="s">
         <v>105</v>
@@ -7974,10 +7974,10 @@
         <v>0</v>
       </c>
       <c r="S95" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T95" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U95">
         <v>136</v>
@@ -7991,7 +7991,7 @@
     </row>
     <row r="96" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B96">
         <v>800</v>
@@ -8000,7 +8000,7 @@
         <v>4900</v>
       </c>
       <c r="D96" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E96">
         <v>0.121</v>
@@ -8009,7 +8009,7 @@
         <v>0.4</v>
       </c>
       <c r="G96" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H96" t="s">
         <v>106</v>
@@ -8039,13 +8039,13 @@
         <v>0</v>
       </c>
       <c r="S96" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T96" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U96" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V96">
         <v>16</v>
@@ -8056,7 +8056,7 @@
     </row>
     <row r="97" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B97">
         <v>290</v>
@@ -8074,7 +8074,7 @@
         <v>0.4</v>
       </c>
       <c r="G97" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H97" t="s">
         <v>107</v>
@@ -8104,13 +8104,13 @@
         <v>0</v>
       </c>
       <c r="S97" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T97" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U97" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V97">
         <v>13</v>
@@ -8121,25 +8121,25 @@
     </row>
     <row r="98" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B98">
         <v>800</v>
       </c>
       <c r="C98" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D98" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E98" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F98" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G98" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H98" t="s">
         <v>108</v>
@@ -8169,51 +8169,51 @@
         <v>1</v>
       </c>
       <c r="S98" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T98" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U98" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V98" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W98" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="99" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B99" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C99" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D99" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E99" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F99" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G99" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H99" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I99" t="s">
         <v>109</v>
       </c>
       <c r="J99" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="K99">
         <v>0</v>
@@ -8240,42 +8240,42 @@
         <v>1</v>
       </c>
       <c r="S99" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T99" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U99" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V99" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W99" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="100" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B100">
         <v>1.4</v>
       </c>
       <c r="C100" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D100" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E100" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F100" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G100" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H100" t="s">
         <v>110</v>
@@ -8305,24 +8305,24 @@
         <v>0</v>
       </c>
       <c r="S100" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T100" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U100" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V100" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W100" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="101" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B101">
         <v>2.5</v>
@@ -8340,7 +8340,7 @@
         <v>0.4</v>
       </c>
       <c r="G101" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H101" t="s">
         <v>111</v>
@@ -8370,10 +8370,10 @@
         <v>0</v>
       </c>
       <c r="S101" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T101" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U101">
         <v>536</v>
@@ -8387,25 +8387,25 @@
     </row>
     <row r="102" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B102">
         <v>14000</v>
       </c>
       <c r="C102" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D102" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E102" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F102" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G102" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H102" t="s">
         <v>112</v>
@@ -8438,42 +8438,42 @@
         <v>1</v>
       </c>
       <c r="S102" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T102" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U102" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V102" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W102" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="103" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B103" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C103" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D103" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E103" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F103" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G103" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H103" t="s">
         <v>114</v>
@@ -8506,42 +8506,42 @@
         <v>0</v>
       </c>
       <c r="S103" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T103" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U103" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V103" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W103" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="104" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B104">
         <v>1</v>
       </c>
       <c r="C104" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D104" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E104" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F104" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G104" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H104" t="s">
         <v>116</v>
@@ -8571,42 +8571,42 @@
         <v>0</v>
       </c>
       <c r="S104" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T104" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U104" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V104" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W104" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="105" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B105">
         <v>430</v>
       </c>
       <c r="C105" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D105" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E105" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F105" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G105" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H105" t="s">
         <v>118</v>
@@ -8639,42 +8639,42 @@
         <v>1</v>
       </c>
       <c r="S105" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T105" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U105" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V105" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W105" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="106" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B106" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C106" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D106" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E106" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F106" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G106" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H106" t="s">
         <v>120</v>
@@ -8707,42 +8707,42 @@
         <v>1</v>
       </c>
       <c r="S106" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T106" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U106" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V106" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W106" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="107" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B107">
         <v>0.63</v>
       </c>
       <c r="C107" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D107" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E107" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F107" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G107" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H107" t="s">
         <v>122</v>
@@ -8775,42 +8775,42 @@
         <v>0</v>
       </c>
       <c r="S107" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T107" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U107" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V107" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W107" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="108" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B108" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C108" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D108" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E108" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F108" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G108" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H108" t="s">
         <v>124</v>
@@ -8840,42 +8840,42 @@
         <v>0</v>
       </c>
       <c r="S108" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T108" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U108" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V108" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W108" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="109" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B109" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C109" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D109" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E109" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F109" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G109" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H109" t="s">
         <v>125</v>
@@ -8905,24 +8905,24 @@
         <v>0</v>
       </c>
       <c r="S109" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T109" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U109" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V109" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W109" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="110" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B110">
         <v>140</v>
@@ -8934,13 +8934,13 @@
         <v>690</v>
       </c>
       <c r="E110" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F110" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G110" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H110" t="s">
         <v>126</v>
@@ -8973,10 +8973,10 @@
         <v>0</v>
       </c>
       <c r="S110" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T110" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U110">
         <v>55</v>
@@ -8990,25 +8990,25 @@
     </row>
     <row r="111" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B111">
         <v>110</v>
       </c>
       <c r="C111" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D111" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E111" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F111" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G111" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H111" t="s">
         <v>128</v>
@@ -9038,42 +9038,42 @@
         <v>0</v>
       </c>
       <c r="S111" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T111" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U111" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V111" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W111" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="112" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B112">
         <v>1000</v>
       </c>
       <c r="C112" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D112" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E112" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F112" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G112" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H112" t="s">
         <v>129</v>
@@ -9103,42 +9103,42 @@
         <v>0</v>
       </c>
       <c r="S112" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T112" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U112" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V112" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W112" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="113" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B113">
         <v>660</v>
       </c>
       <c r="C113" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D113" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E113" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F113" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G113" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H113" t="s">
         <v>130</v>
@@ -9168,24 +9168,24 @@
         <v>0</v>
       </c>
       <c r="S113" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T113" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U113" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V113" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W113" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="114" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B114">
         <v>1.2</v>
@@ -9203,7 +9203,7 @@
         <v>0.4</v>
       </c>
       <c r="G114" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H114" t="s">
         <v>131</v>
@@ -9233,13 +9233,13 @@
         <v>0</v>
       </c>
       <c r="S114" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T114" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U114" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V114">
         <v>10</v>
@@ -9250,25 +9250,25 @@
     </row>
     <row r="115" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B115">
         <v>390</v>
       </c>
       <c r="C115" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D115" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E115" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F115" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G115" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H115" t="s">
         <v>132</v>
@@ -9298,51 +9298,51 @@
         <v>0</v>
       </c>
       <c r="S115" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T115" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U115" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V115" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W115" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="116" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B116">
         <v>2000</v>
       </c>
       <c r="C116" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D116" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E116" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F116" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G116" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H116" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I116" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J116" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K116">
         <v>0</v>
@@ -9369,51 +9369,51 @@
         <v>1</v>
       </c>
       <c r="S116" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T116" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U116" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V116" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W116" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="117" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B117">
         <v>32000</v>
       </c>
       <c r="C117" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D117" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E117" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F117" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G117" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H117" t="s">
+        <v>134</v>
+      </c>
+      <c r="I117" t="s">
         <v>135</v>
       </c>
-      <c r="I117" t="s">
-        <v>136</v>
-      </c>
       <c r="J117" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K117">
         <v>0</v>
@@ -9440,45 +9440,45 @@
         <v>1</v>
       </c>
       <c r="S117" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T117" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U117" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V117" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W117" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="118" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B118">
         <v>240</v>
       </c>
       <c r="C118" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D118" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E118" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F118" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G118" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H118" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K118">
         <v>0</v>
@@ -9505,24 +9505,24 @@
         <v>0</v>
       </c>
       <c r="S118" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T118" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U118" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V118" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W118" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="119" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B119">
         <v>190</v>
@@ -9534,16 +9534,16 @@
         <v>260</v>
       </c>
       <c r="E119" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F119" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G119" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H119" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K119">
         <v>0</v>
@@ -9570,13 +9570,13 @@
         <v>0</v>
       </c>
       <c r="S119" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T119" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U119" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V119">
         <v>8</v>
@@ -9587,25 +9587,25 @@
     </row>
     <row r="120" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B120" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C120" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D120" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E120" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F120" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G120" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="K120">
         <v>0</v>
@@ -9632,45 +9632,45 @@
         <v>0</v>
       </c>
       <c r="S120" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T120" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U120" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V120" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W120" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="121" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B121">
         <v>250</v>
       </c>
       <c r="C121" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D121" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E121" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F121" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G121" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H121" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K121">
         <v>0</v>
@@ -9697,45 +9697,45 @@
         <v>0</v>
       </c>
       <c r="S121" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T121" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U121" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V121" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W121" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="122" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B122" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C122" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D122" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E122" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F122" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G122" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H122" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K122">
         <v>0</v>
@@ -9762,24 +9762,24 @@
         <v>0</v>
       </c>
       <c r="S122" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T122" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U122" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V122" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W122" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="123" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B123">
         <v>190</v>
@@ -9791,16 +9791,16 @@
         <v>260</v>
       </c>
       <c r="E123" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F123" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G123" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H123" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I123" t="s">
         <v>117</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="S123" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T123" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U123">
         <v>139</v>
@@ -9847,28 +9847,28 @@
     </row>
     <row r="124" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B124" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C124" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D124" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E124" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F124" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G124" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H124" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K124">
         <v>0</v>
@@ -9895,24 +9895,24 @@
         <v>1</v>
       </c>
       <c r="S124" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T124" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U124" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V124" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W124" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="125" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B125">
         <v>180</v>
@@ -9921,7 +9921,7 @@
         <v>320</v>
       </c>
       <c r="D125" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E125">
         <v>8.4000000000000005E-2</v>
@@ -9930,10 +9930,10 @@
         <v>0.4</v>
       </c>
       <c r="G125" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H125" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K125">
         <v>1</v>
@@ -9960,13 +9960,13 @@
         <v>0</v>
       </c>
       <c r="S125" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T125" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U125" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V125">
         <v>14</v>
@@ -9977,32 +9977,32 @@
     </row>
     <row r="126" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B126" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C126" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D126" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E126" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F126" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G126" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H126" t="s">
+        <v>144</v>
+      </c>
+      <c r="I126" t="s">
         <v>145</v>
       </c>
-      <c r="I126" t="s">
-        <v>146</v>
-      </c>
       <c r="K126">
         <v>0</v>
       </c>
@@ -10028,24 +10028,24 @@
         <v>0</v>
       </c>
       <c r="S126" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T126" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U126" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V126" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W126" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="127" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B127">
         <v>120</v>
@@ -10063,10 +10063,10 @@
         <v>0.4</v>
       </c>
       <c r="G127" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H127" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K127">
         <v>1</v>
@@ -10093,13 +10093,13 @@
         <v>0</v>
       </c>
       <c r="S127" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T127" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U127" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V127">
         <v>16</v>
@@ -10110,28 +10110,28 @@
     </row>
     <row r="128" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B128" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C128" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D128" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E128" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F128" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G128" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H128" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K128">
         <v>0</v>
@@ -10158,45 +10158,45 @@
         <v>1</v>
       </c>
       <c r="S128" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T128" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U128" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V128" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W128" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="129" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B129">
         <v>100</v>
       </c>
       <c r="C129" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D129" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E129" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F129" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G129" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H129" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K129">
         <v>0</v>
@@ -10223,45 +10223,45 @@
         <v>0</v>
       </c>
       <c r="S129" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T129" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U129" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V129" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W129" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="130" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B130">
         <v>2000</v>
       </c>
       <c r="C130" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D130" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E130" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F130" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G130" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H130" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K130">
         <v>0</v>
@@ -10288,45 +10288,45 @@
         <v>0</v>
       </c>
       <c r="S130" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T130" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U130" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V130" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W130" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="131" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B131">
         <v>94</v>
       </c>
       <c r="C131" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D131" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E131" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F131" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G131" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H131" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K131">
         <v>0</v>
@@ -10353,45 +10353,45 @@
         <v>0</v>
       </c>
       <c r="S131" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T131" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U131" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V131" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W131" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="132" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B132">
         <v>500</v>
       </c>
       <c r="C132" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D132" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E132" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F132" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G132" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H132" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K132">
         <v>0</v>
@@ -10418,49 +10418,49 @@
         <v>0</v>
       </c>
       <c r="S132" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T132" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U132" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V132" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W132" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="133" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B133" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C133" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D133" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E133" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F133" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G133" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H133" t="s">
+        <v>152</v>
+      </c>
+      <c r="I133" t="s">
         <v>153</v>
       </c>
-      <c r="I133" t="s">
-        <v>154</v>
-      </c>
       <c r="K133">
         <v>0</v>
       </c>
@@ -10486,45 +10486,45 @@
         <v>0</v>
       </c>
       <c r="S133" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T133" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U133" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V133" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W133" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="134" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B134" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C134" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D134" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E134" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F134" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G134" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H134" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K134">
         <v>0</v>
@@ -10551,45 +10551,45 @@
         <v>0</v>
       </c>
       <c r="S134" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T134" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U134" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V134" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W134" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="135" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B135">
         <v>1200</v>
       </c>
       <c r="C135" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D135" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E135" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F135" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G135" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H135" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K135">
         <v>0</v>
@@ -10616,45 +10616,45 @@
         <v>0</v>
       </c>
       <c r="S135" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T135" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U135" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V135" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W135" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="136" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B136" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C136" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D136" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E136" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F136" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G136" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H136" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K136">
         <v>0</v>
@@ -10681,45 +10681,45 @@
         <v>0</v>
       </c>
       <c r="S136" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T136" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U136" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V136" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W136" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="137" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B137" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C137" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D137" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E137" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F137" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G137" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H137" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K137">
         <v>0</v>
@@ -10746,45 +10746,45 @@
         <v>0</v>
       </c>
       <c r="S137" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T137" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U137" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V137" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W137" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="138" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B138">
         <v>690</v>
       </c>
       <c r="C138" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D138" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E138" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F138" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G138" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H138" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K138">
         <v>0</v>
@@ -10811,45 +10811,45 @@
         <v>0</v>
       </c>
       <c r="S138" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T138" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U138" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V138" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W138" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="139" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B139" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C139" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D139" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E139" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F139" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G139" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H139" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K139">
         <v>0</v>
@@ -10876,45 +10876,45 @@
         <v>0</v>
       </c>
       <c r="S139" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T139" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U139" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V139" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W139" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="140" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B140">
         <v>41</v>
       </c>
       <c r="C140" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D140" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E140" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F140" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G140" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H140" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K140">
         <v>0</v>
@@ -10941,45 +10941,45 @@
         <v>0</v>
       </c>
       <c r="S140" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T140" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U140" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V140" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W140" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="141" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B141">
         <v>3400</v>
       </c>
       <c r="C141" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D141" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E141" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F141" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G141" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H141" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K141">
         <v>0</v>
@@ -11006,45 +11006,45 @@
         <v>0</v>
       </c>
       <c r="S141" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T141" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U141" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V141" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W141" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="142" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B142">
         <v>0.2</v>
       </c>
       <c r="C142" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D142" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E142" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F142" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G142" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H142" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K142">
         <v>0</v>
@@ -11071,24 +11071,24 @@
         <v>0</v>
       </c>
       <c r="S142" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T142" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U142" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V142" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W142" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="143" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B143">
         <v>1100</v>
@@ -11100,16 +11100,16 @@
         <v>750</v>
       </c>
       <c r="E143" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F143" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G143" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H143" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K143">
         <v>0</v>
@@ -11136,13 +11136,13 @@
         <v>0</v>
       </c>
       <c r="S143" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T143" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U143" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V143">
         <v>7</v>
@@ -11153,28 +11153,28 @@
     </row>
     <row r="144" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B144" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C144" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D144" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E144" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F144" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G144" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H144" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K144">
         <v>0</v>
@@ -11201,48 +11201,48 @@
         <v>0</v>
       </c>
       <c r="S144" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T144" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U144" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V144" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W144" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="145" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B145" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C145" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D145" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E145" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F145" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G145" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H145" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I145" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K145">
         <v>0</v>
@@ -11269,80 +11269,80 @@
         <v>1</v>
       </c>
       <c r="S145" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T145" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U145" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V145" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W145" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="146" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
+        <v>440</v>
+      </c>
+      <c r="B146" t="s">
+        <v>420</v>
+      </c>
+      <c r="C146" t="s">
+        <v>420</v>
+      </c>
+      <c r="D146" t="s">
+        <v>420</v>
+      </c>
+      <c r="E146" t="s">
+        <v>420</v>
+      </c>
+      <c r="F146" t="s">
+        <v>420</v>
+      </c>
+      <c r="G146" t="s">
+        <v>420</v>
+      </c>
+      <c r="H146" t="s">
         <v>441</v>
       </c>
-      <c r="B146" t="s">
-        <v>421</v>
-      </c>
-      <c r="C146" t="s">
-        <v>421</v>
-      </c>
-      <c r="D146" t="s">
-        <v>421</v>
-      </c>
-      <c r="E146" t="s">
-        <v>421</v>
-      </c>
-      <c r="F146" t="s">
-        <v>421</v>
-      </c>
-      <c r="G146" t="s">
-        <v>421</v>
-      </c>
-      <c r="H146" t="s">
-        <v>442</v>
-      </c>
       <c r="U146" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V146" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W146" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="147" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B147">
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="C147" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D147" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E147" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F147" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G147" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H147" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K147">
         <v>0</v>
@@ -11369,45 +11369,45 @@
         <v>0</v>
       </c>
       <c r="S147" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T147" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U147" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V147" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W147" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="148" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B148" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C148" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D148" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E148" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F148" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G148" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H148" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K148">
         <v>0</v>
@@ -11434,45 +11434,45 @@
         <v>0</v>
       </c>
       <c r="S148" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T148" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U148" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V148" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W148" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="149" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B149">
         <v>2.8</v>
       </c>
       <c r="C149" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D149" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E149" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F149" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G149" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H149" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K149">
         <v>0</v>
@@ -11499,45 +11499,45 @@
         <v>0</v>
       </c>
       <c r="S149" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T149" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U149" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V149" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W149" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="150" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B150">
         <v>5200</v>
       </c>
       <c r="C150" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D150" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E150" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F150" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G150" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H150" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K150">
         <v>0</v>
@@ -11564,45 +11564,45 @@
         <v>0</v>
       </c>
       <c r="S150" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T150" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U150" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V150" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W150" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="151" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B151" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C151" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D151" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E151" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F151" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G151" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H151" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K151">
         <v>0</v>
@@ -11629,45 +11629,45 @@
         <v>0</v>
       </c>
       <c r="S151" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T151" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U151" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V151" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W151" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="152" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B152">
         <v>86</v>
       </c>
       <c r="C152" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D152" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E152" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F152" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G152" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H152" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K152">
         <v>0</v>
@@ -11694,45 +11694,45 @@
         <v>0</v>
       </c>
       <c r="S152" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T152" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U152" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V152" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W152" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="153" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B153">
         <v>410</v>
       </c>
       <c r="C153" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D153" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E153" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F153" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G153" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H153" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K153">
         <v>0</v>
@@ -11759,45 +11759,45 @@
         <v>0</v>
       </c>
       <c r="S153" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T153" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U153" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V153" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W153" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="154" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B154">
         <v>0.19</v>
       </c>
       <c r="C154" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D154" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E154" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F154" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G154" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H154" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K154">
         <v>0</v>
@@ -11824,45 +11824,45 @@
         <v>0</v>
       </c>
       <c r="S154" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T154" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U154" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V154" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W154" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B155">
         <v>190</v>
       </c>
       <c r="C155" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D155" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E155" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F155" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G155" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H155" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K155">
         <v>0</v>
@@ -11889,45 +11889,45 @@
         <v>0</v>
       </c>
       <c r="S155" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T155" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U155" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V155" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W155" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B156">
         <v>6000</v>
       </c>
       <c r="C156" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D156" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E156" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F156" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G156" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H156" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K156">
         <v>0</v>
@@ -11954,33 +11954,33 @@
         <v>0</v>
       </c>
       <c r="S156" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T156" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U156" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V156" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W156" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B157" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C157" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D157" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E157">
         <v>0.34599999999999997</v>
@@ -11989,13 +11989,13 @@
         <v>1.92</v>
       </c>
       <c r="G157" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H157" t="s">
+        <v>183</v>
+      </c>
+      <c r="I157" t="s">
         <v>184</v>
-      </c>
-      <c r="I157" t="s">
-        <v>185</v>
       </c>
       <c r="K157">
         <v>0</v>
@@ -12028,27 +12028,27 @@
         <v>7</v>
       </c>
       <c r="U157" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V157" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W157" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B158" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C158" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E158">
         <v>0.46600000000000003</v>
@@ -12057,13 +12057,13 @@
         <v>1.92</v>
       </c>
       <c r="G158" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H158" t="s">
+        <v>185</v>
+      </c>
+      <c r="I158" t="s">
         <v>186</v>
-      </c>
-      <c r="I158" t="s">
-        <v>187</v>
       </c>
       <c r="K158">
         <v>0</v>
@@ -12096,27 +12096,27 @@
         <v>6</v>
       </c>
       <c r="U158" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V158" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W158" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="159" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B159" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C159" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E159">
         <v>1.37</v>
@@ -12125,13 +12125,13 @@
         <v>1.92</v>
       </c>
       <c r="G159" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H159" t="s">
+        <v>187</v>
+      </c>
+      <c r="I159" t="s">
         <v>188</v>
-      </c>
-      <c r="I159" t="s">
-        <v>189</v>
       </c>
       <c r="K159">
         <v>0</v>
@@ -12164,27 +12164,27 @@
         <v>8</v>
       </c>
       <c r="U159" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V159" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W159" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="160" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B160" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C160" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D160" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E160">
         <v>1.25</v>
@@ -12193,13 +12193,13 @@
         <v>1.92</v>
       </c>
       <c r="G160" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H160" t="s">
+        <v>189</v>
+      </c>
+      <c r="I160" t="s">
         <v>190</v>
-      </c>
-      <c r="I160" t="s">
-        <v>191</v>
       </c>
       <c r="K160">
         <v>0</v>
@@ -12232,21 +12232,21 @@
         <v>10</v>
       </c>
       <c r="U160" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V160" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W160" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="161" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B161" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C161">
         <v>0.81</v>
@@ -12264,10 +12264,10 @@
         <v>10</v>
       </c>
       <c r="H161" t="s">
+        <v>191</v>
+      </c>
+      <c r="I161" t="s">
         <v>192</v>
-      </c>
-      <c r="I161" t="s">
-        <v>193</v>
       </c>
       <c r="K161">
         <v>0</v>
@@ -12300,27 +12300,27 @@
         <v>3</v>
       </c>
       <c r="U161" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V161" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W161" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="162" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B162" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C162" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D162" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E162">
         <v>0.82899999999999996</v>
@@ -12329,13 +12329,13 @@
         <v>1.92</v>
       </c>
       <c r="G162" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H162" t="s">
+        <v>193</v>
+      </c>
+      <c r="I162" t="s">
         <v>194</v>
-      </c>
-      <c r="I162" t="s">
-        <v>195</v>
       </c>
       <c r="K162">
         <v>0</v>
@@ -12368,27 +12368,27 @@
         <v>8</v>
       </c>
       <c r="U162" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V162" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W162" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="163" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B163" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C163" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D163" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E163">
         <v>0.66800000000000004</v>
@@ -12397,13 +12397,13 @@
         <v>1.92</v>
       </c>
       <c r="G163" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H163" t="s">
+        <v>195</v>
+      </c>
+      <c r="I163" t="s">
         <v>196</v>
-      </c>
-      <c r="I163" t="s">
-        <v>197</v>
       </c>
       <c r="K163">
         <v>0</v>
@@ -12436,18 +12436,18 @@
         <v>8</v>
       </c>
       <c r="U163" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V163" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W163" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="164" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B164">
         <v>6000</v>
@@ -12465,13 +12465,13 @@
         <v>1.92</v>
       </c>
       <c r="G164" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H164" t="s">
+        <v>197</v>
+      </c>
+      <c r="I164" t="s">
         <v>198</v>
-      </c>
-      <c r="I164" t="s">
-        <v>199</v>
       </c>
       <c r="K164">
         <v>0</v>
@@ -12504,18 +12504,18 @@
         <v>4</v>
       </c>
       <c r="U164" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V164" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W164" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="165" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B165">
         <v>19000</v>
@@ -12533,13 +12533,13 @@
         <v>1.92</v>
       </c>
       <c r="G165" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H165" t="s">
+        <v>199</v>
+      </c>
+      <c r="I165" t="s">
         <v>200</v>
-      </c>
-      <c r="I165" t="s">
-        <v>201</v>
       </c>
       <c r="K165">
         <v>0</v>
@@ -12572,27 +12572,27 @@
         <v>4</v>
       </c>
       <c r="U165" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V165" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W165" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="166" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B166" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C166" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D166" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E166">
         <v>1.01</v>
@@ -12601,13 +12601,13 @@
         <v>1.92</v>
       </c>
       <c r="G166" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H166" t="s">
+        <v>201</v>
+      </c>
+      <c r="I166" t="s">
         <v>202</v>
-      </c>
-      <c r="I166" t="s">
-        <v>203</v>
       </c>
       <c r="K166">
         <v>0</v>
@@ -12640,27 +12640,27 @@
         <v>10</v>
       </c>
       <c r="U166" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V166" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W166" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="167" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B167" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C167" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D167" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E167">
         <v>0.313</v>
@@ -12669,13 +12669,13 @@
         <v>1.92</v>
       </c>
       <c r="G167" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H167" t="s">
+        <v>203</v>
+      </c>
+      <c r="I167" t="s">
         <v>204</v>
-      </c>
-      <c r="I167" t="s">
-        <v>205</v>
       </c>
       <c r="K167">
         <v>0</v>
@@ -12708,27 +12708,27 @@
         <v>10</v>
       </c>
       <c r="U167" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V167" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W167" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="168" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B168" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C168" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D168" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E168">
         <v>0.38400000000000001</v>
@@ -12737,13 +12737,13 @@
         <v>3.84</v>
       </c>
       <c r="G168" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H168" t="s">
+        <v>205</v>
+      </c>
+      <c r="I168" t="s">
         <v>206</v>
-      </c>
-      <c r="I168" t="s">
-        <v>207</v>
       </c>
       <c r="K168">
         <v>0</v>
@@ -12776,27 +12776,27 @@
         <v>12</v>
       </c>
       <c r="U168" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V168" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W168" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="169" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B169" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C169" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D169" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E169">
         <v>0.70899999999999996</v>
@@ -12805,13 +12805,13 @@
         <v>1.92</v>
       </c>
       <c r="G169" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H169" t="s">
+        <v>207</v>
+      </c>
+      <c r="I169" t="s">
         <v>208</v>
-      </c>
-      <c r="I169" t="s">
-        <v>209</v>
       </c>
       <c r="K169">
         <v>0</v>
@@ -12844,27 +12844,27 @@
         <v>7</v>
       </c>
       <c r="U169" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V169" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W169" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="170" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B170" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C170" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D170" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E170">
         <v>0.23200000000000001</v>
@@ -12873,13 +12873,13 @@
         <v>1.92</v>
       </c>
       <c r="G170" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H170" t="s">
+        <v>209</v>
+      </c>
+      <c r="I170" t="s">
         <v>210</v>
-      </c>
-      <c r="I170" t="s">
-        <v>211</v>
       </c>
       <c r="K170">
         <v>0</v>
@@ -12912,27 +12912,27 @@
         <v>7</v>
       </c>
       <c r="U170" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V170" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W170" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="171" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B171" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C171" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D171" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E171">
         <v>1.28</v>
@@ -12941,13 +12941,13 @@
         <v>3.84</v>
       </c>
       <c r="G171" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H171" t="s">
+        <v>211</v>
+      </c>
+      <c r="I171" t="s">
         <v>212</v>
-      </c>
-      <c r="I171" t="s">
-        <v>213</v>
       </c>
       <c r="K171">
         <v>0</v>
@@ -12980,18 +12980,18 @@
         <v>6</v>
       </c>
       <c r="U171" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V171" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W171" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="172" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B172">
         <v>390</v>
@@ -13012,10 +13012,10 @@
         <v>10</v>
       </c>
       <c r="H172" t="s">
+        <v>213</v>
+      </c>
+      <c r="I172" t="s">
         <v>214</v>
-      </c>
-      <c r="I172" t="s">
-        <v>215</v>
       </c>
       <c r="K172">
         <v>0</v>
@@ -13048,18 +13048,18 @@
         <v>6</v>
       </c>
       <c r="U172" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V172" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W172" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="173" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B173">
         <v>9900</v>
@@ -13077,13 +13077,13 @@
         <v>1.92</v>
       </c>
       <c r="G173" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H173" t="s">
+        <v>215</v>
+      </c>
+      <c r="I173" t="s">
         <v>216</v>
-      </c>
-      <c r="I173" t="s">
-        <v>217</v>
       </c>
       <c r="K173">
         <v>0</v>
@@ -13116,27 +13116,27 @@
         <v>6</v>
       </c>
       <c r="U173" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V173" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W173" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="174" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B174" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C174" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D174" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E174">
         <v>1.1499999999999999</v>
@@ -13145,13 +13145,13 @@
         <v>1.92</v>
       </c>
       <c r="G174" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H174" t="s">
+        <v>217</v>
+      </c>
+      <c r="I174" t="s">
         <v>218</v>
-      </c>
-      <c r="I174" t="s">
-        <v>219</v>
       </c>
       <c r="K174">
         <v>0</v>
@@ -13184,18 +13184,18 @@
         <v>9</v>
       </c>
       <c r="U174" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V174" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W174" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="175" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B175">
         <v>59</v>
@@ -13216,10 +13216,10 @@
         <v>10</v>
       </c>
       <c r="H175" t="s">
+        <v>219</v>
+      </c>
+      <c r="I175" t="s">
         <v>220</v>
-      </c>
-      <c r="I175" t="s">
-        <v>221</v>
       </c>
       <c r="K175">
         <v>0</v>
@@ -13252,27 +13252,27 @@
         <v>9</v>
       </c>
       <c r="U175" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V175" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W175" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="176" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B176" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C176" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D176" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E176">
         <v>1.18</v>
@@ -13281,13 +13281,13 @@
         <v>1.92</v>
       </c>
       <c r="G176" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H176" t="s">
+        <v>221</v>
+      </c>
+      <c r="I176" t="s">
         <v>222</v>
-      </c>
-      <c r="I176" t="s">
-        <v>223</v>
       </c>
       <c r="K176">
         <v>0</v>
@@ -13320,27 +13320,27 @@
         <v>18</v>
       </c>
       <c r="U176" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V176" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W176" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="177" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B177" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C177" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D177" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E177">
         <v>0.59799999999999998</v>
@@ -13349,13 +13349,13 @@
         <v>1.92</v>
       </c>
       <c r="G177" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H177" t="s">
+        <v>223</v>
+      </c>
+      <c r="I177" t="s">
         <v>224</v>
-      </c>
-      <c r="I177" t="s">
-        <v>225</v>
       </c>
       <c r="K177">
         <v>0</v>
@@ -13388,18 +13388,18 @@
         <v>8</v>
       </c>
       <c r="U177" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V177" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W177" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="178" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B178">
         <v>40</v>
@@ -13420,10 +13420,10 @@
         <v>4</v>
       </c>
       <c r="H178" t="s">
+        <v>225</v>
+      </c>
+      <c r="I178" t="s">
         <v>226</v>
-      </c>
-      <c r="I178" t="s">
-        <v>227</v>
       </c>
       <c r="K178">
         <v>0</v>
@@ -13456,18 +13456,18 @@
         <v>8</v>
       </c>
       <c r="U178" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V178" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W178" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="179" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B179">
         <v>60</v>
@@ -13488,10 +13488,10 @@
         <v>4</v>
       </c>
       <c r="H179" t="s">
+        <v>227</v>
+      </c>
+      <c r="I179" t="s">
         <v>228</v>
-      </c>
-      <c r="I179" t="s">
-        <v>229</v>
       </c>
       <c r="K179">
         <v>0</v>
@@ -13524,27 +13524,27 @@
         <v>8</v>
       </c>
       <c r="U179" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V179" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W179" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="180" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B180" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C180" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D180" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E180">
         <v>0.253</v>
@@ -13553,13 +13553,13 @@
         <v>1.92</v>
       </c>
       <c r="G180" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H180" t="s">
+        <v>229</v>
+      </c>
+      <c r="I180" t="s">
         <v>230</v>
-      </c>
-      <c r="I180" t="s">
-        <v>231</v>
       </c>
       <c r="K180">
         <v>0</v>
@@ -13592,27 +13592,27 @@
         <v>5</v>
       </c>
       <c r="U180" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V180" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W180" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="181" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B181" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C181" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D181" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E181">
         <v>0.40799999999999997</v>
@@ -13621,13 +13621,13 @@
         <v>1.92</v>
       </c>
       <c r="G181" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H181" t="s">
+        <v>231</v>
+      </c>
+      <c r="I181" t="s">
         <v>232</v>
-      </c>
-      <c r="I181" t="s">
-        <v>233</v>
       </c>
       <c r="K181">
         <v>0</v>
@@ -13660,27 +13660,27 @@
         <v>5</v>
       </c>
       <c r="U181" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V181" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W181" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="182" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B182" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C182" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D182" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E182">
         <v>0.25600000000000001</v>
@@ -13689,13 +13689,13 @@
         <v>1.92</v>
       </c>
       <c r="G182" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H182" t="s">
+        <v>233</v>
+      </c>
+      <c r="I182" t="s">
         <v>234</v>
-      </c>
-      <c r="I182" t="s">
-        <v>235</v>
       </c>
       <c r="K182">
         <v>0</v>
@@ -13728,27 +13728,27 @@
         <v>14</v>
       </c>
       <c r="U182" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V182" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W182" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="183" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B183" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C183" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D183" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E183">
         <v>0.33700000000000002</v>
@@ -13757,13 +13757,13 @@
         <v>1.92</v>
       </c>
       <c r="G183" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H183" t="s">
+        <v>235</v>
+      </c>
+      <c r="I183" t="s">
         <v>236</v>
-      </c>
-      <c r="I183" t="s">
-        <v>237</v>
       </c>
       <c r="K183">
         <v>0</v>
@@ -13796,27 +13796,27 @@
         <v>13</v>
       </c>
       <c r="U183" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V183" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W183" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="184" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B184" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C184" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D184" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E184">
         <v>0.26800000000000002</v>
@@ -13825,13 +13825,13 @@
         <v>1.92</v>
       </c>
       <c r="G184" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H184" t="s">
+        <v>237</v>
+      </c>
+      <c r="I184" t="s">
         <v>238</v>
-      </c>
-      <c r="I184" t="s">
-        <v>239</v>
       </c>
       <c r="K184">
         <v>0</v>
@@ -13864,43 +13864,43 @@
         <v>11</v>
       </c>
       <c r="U184" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V184" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W184" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="185" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B185">
         <v>20</v>
       </c>
       <c r="C185" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D185" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E185" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F185" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G185" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H185" t="s">
+        <v>239</v>
+      </c>
+      <c r="I185" t="s">
         <v>240</v>
       </c>
-      <c r="I185" t="s">
-        <v>241</v>
-      </c>
       <c r="K185">
         <v>0</v>
       </c>
@@ -13926,19 +13926,19 @@
         <v>0</v>
       </c>
       <c r="S185" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T185" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U185" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="V185" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="W185" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>
